--- a/excel/100000(n)/RAW_Dataset.xlsx
+++ b/excel/100000(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,43 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +419,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +433,142 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.30607581E10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.30030595E10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>1.2813318E9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>1.2609032E9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.4395654E9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.4338476E9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.51161E7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>1.61649E7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>2.11579E7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>3.14808E7</v>
       </c>
     </row>
   </sheetData>

--- a/excel/100000(n)/RAW_Dataset.xlsx
+++ b/excel/100000(n)/RAW_Dataset.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="14.77734375"/>
@@ -460,6 +463,9 @@
       <c r="K1" t="s" s="0">
         <v>10</v>
       </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
@@ -469,7 +475,34 @@
         <v>100000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>1.30607581E10</v>
+        <v>1.24851533E10</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.24349686E10</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>1.10570388E10</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>1.10195901E10</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>1.10675742E10</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>1.1037788E10</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>1.16030417E10</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>1.10363493E10</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>1.14560086E10</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>1.10924674E10</v>
       </c>
     </row>
     <row r="3">
@@ -480,7 +513,34 @@
         <v>100000.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>1.30030595E10</v>
+        <v>1.24564842E10</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.24770923E10</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.10690259E10</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.10950992E10</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>1.11413456E10</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>1.10214588E10</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>1.11614788E10</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>1.11779481E10</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>1.14508797E10</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>1.10593269E10</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +551,34 @@
         <v>100000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1.2813318E9</v>
+        <v>1.2261227E9</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.2815997E9</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>1.2862525E9</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>3.810008E8</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>3.880474E8</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>3.871775E8</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>3.913965E8</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>3.926075E8</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>3.88053E8</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>3.883985E8</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +589,34 @@
         <v>100000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>1.2609032E9</v>
+        <v>1.2298982E9</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.2765147E9</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.2743331E9</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>3.921814E8</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>3.933931E8</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>3.843906E8</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>3.962655E8</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>3.879113E8</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>3.902992E8</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>3.911722E8</v>
       </c>
     </row>
     <row r="6">
@@ -513,7 +627,34 @@
         <v>100000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>2.4395654E9</v>
+        <v>2.3358215E9</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>2.9997969E9</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>1.3225229E9</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>1.3124474E9</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>1.3060503E9</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>1.3075353E9</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>1.3145437E9</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>1.3924715E9</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>1.3152005E9</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>1.3185306E9</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +665,34 @@
         <v>100000.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>2.4338476E9</v>
+        <v>2.328273E9</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>2.3359183E9</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>1.3312722E9</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>1.3290027E9</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>1.3206378E9</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>1.3382492E9</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>1.3239099E9</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>1.3861309E9</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>1.3529562E9</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>1.329176E9</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +703,34 @@
         <v>100000.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>5.51161E7</v>
+        <v>3.08313E7</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>5.12113E7</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>2.763E7</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>9395200.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>1.09786E7</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>9374200.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>9199600.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>9805800.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>9428100.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>6.12438E7</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +741,34 @@
         <v>100000.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>1.61649E7</v>
+        <v>1.52243E7</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>9718400.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>1.14363E7</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>9327000.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>6.38539E7</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>9295300.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>9385300.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>9660500.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>9731700.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>1.0032E7</v>
       </c>
     </row>
     <row r="10">
@@ -557,7 +779,34 @@
         <v>100000.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>2.11579E7</v>
+        <v>1.90492E7</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>1.3834E7</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1.42556E7</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>1.08943E7</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>1.38522E7</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>1.06654E7</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>1.03986E7</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>1.06335E7</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>1.07943E7</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>1.4537E7</v>
       </c>
     </row>
     <row r="11">
@@ -568,7 +817,34 @@
         <v>100000.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>3.14808E7</v>
+        <v>4.59568E7</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>2.15696E7</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1.34955E7</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>1.07014E7</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>1.36468E7</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>5.13009E7</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>1.14336E7</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>1.03471E7</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>6.25429E7</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>1.37924E7</v>
       </c>
     </row>
   </sheetData>
